--- a/Treinamento/Planilha Robô Descarte (1).xlsx
+++ b/Treinamento/Planilha Robô Descarte (1).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\WWG00M.ROOTDOM.NET\BFS-HOME\BE03856-R0260586\ICM\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B794B76B-A65D-434A-9EFF-510C8F875F8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6C35D14-8400-4FED-9AD1-E6C886C72328}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{5941E9CA-B087-4FE8-B1CB-F0F427193C50}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="5">
   <si>
     <t>Recibo</t>
   </si>
@@ -47,16 +47,10 @@
     <t xml:space="preserve">CANCELADO - ANALISAR SE DEVE SER DEVOLVIDO             </t>
   </si>
   <si>
-    <t xml:space="preserve">PAGO A MAIOR NÃO BAIXADO - BAIXAR MANUALMENTE          </t>
-  </si>
-  <si>
     <t xml:space="preserve">DUPLICIDADE - ANALISAR SE DEVE SER DEVOLVIDO           </t>
   </si>
   <si>
     <t xml:space="preserve">DUPLICIDADE - CRÉDITO RECEBIDO EM D/C E BOLETO         </t>
-  </si>
-  <si>
-    <t xml:space="preserve">PAGO A MENOR NÃO BAIXADO - BAIXAR MANUALMENTE          </t>
   </si>
 </sst>
 </file>
@@ -156,12 +150,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="8">
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
+  <dxfs count="6">
     <dxf>
       <font>
         <color rgb="FFFF0000"/>
@@ -186,11 +175,6 @@
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
     </dxf>
     <dxf>
       <font>
@@ -529,1500 +513,860 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2">
-        <v>740215318</v>
-      </c>
-      <c r="B2" s="5" t="s">
+        <v>692971405</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3">
-        <v>741358638</v>
-      </c>
-      <c r="B3" t="s">
-        <v>3</v>
+        <v>706987710</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4">
-        <v>626538270</v>
-      </c>
-      <c r="B4" t="s">
-        <v>4</v>
+        <v>804167918</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5">
-        <v>685933149</v>
-      </c>
-      <c r="B5" t="s">
-        <v>4</v>
+        <v>802441364</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6">
-        <v>698974064</v>
-      </c>
-      <c r="B6" t="s">
-        <v>4</v>
+        <v>792490074</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7">
-        <v>730713389</v>
-      </c>
-      <c r="B7" t="s">
-        <v>5</v>
+        <v>786172894</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8">
-        <v>747350043</v>
-      </c>
-      <c r="B8" t="s">
-        <v>4</v>
+        <v>762835720</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A9">
-        <v>753520224</v>
-      </c>
-      <c r="B9" t="s">
+        <v>754007163</v>
+      </c>
+      <c r="B9" s="3" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10">
-        <v>765599034</v>
-      </c>
-      <c r="B10" t="s">
+        <v>748785809</v>
+      </c>
+      <c r="B10" s="3" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A11">
-        <v>718504255</v>
-      </c>
-      <c r="B11" t="s">
+        <v>745399067</v>
+      </c>
+      <c r="B11" s="3" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A12">
-        <v>709041267</v>
-      </c>
-      <c r="B12" t="s">
+        <v>737021752</v>
+      </c>
+      <c r="B12" s="3" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A13">
-        <v>795449606</v>
-      </c>
-      <c r="B13" t="s">
-        <v>4</v>
+        <v>654757008</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A14">
-        <v>611540034</v>
-      </c>
-      <c r="B14" t="s">
-        <v>4</v>
+        <v>647430820</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A15">
-        <v>175289499</v>
+        <v>647430812</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A16">
-        <v>704686090</v>
+        <v>594000626</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A17">
-        <v>738611122</v>
-      </c>
-      <c r="B17" t="s">
-        <v>5</v>
+        <v>594000618</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A18">
-        <v>723317974</v>
-      </c>
-      <c r="B18" t="s">
-        <v>5</v>
+        <v>599078221</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A19">
-        <v>760406060</v>
-      </c>
-      <c r="B19" t="s">
-        <v>5</v>
+        <v>785689492</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A20">
-        <v>770207243</v>
-      </c>
-      <c r="B20" t="s">
-        <v>5</v>
+        <v>794816169</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A21">
-        <v>663969149</v>
-      </c>
-      <c r="B21" t="s">
-        <v>5</v>
+        <v>811797814</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A22">
-        <v>763739970</v>
-      </c>
-      <c r="B22" t="s">
-        <v>5</v>
+        <v>810874572</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A23">
-        <v>795052434</v>
-      </c>
-      <c r="B23" t="s">
-        <v>2</v>
+        <v>801792916</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A24">
-        <v>790299261</v>
-      </c>
-      <c r="B24" t="s">
-        <v>2</v>
+        <v>784734950</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A25">
-        <v>787001019</v>
-      </c>
-      <c r="B25" t="s">
-        <v>2</v>
+        <v>783361086</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A26">
-        <v>786979983</v>
-      </c>
-      <c r="B26" t="s">
-        <v>2</v>
+        <v>610137261</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A27">
-        <v>669240644</v>
-      </c>
-      <c r="B27" t="s">
-        <v>2</v>
+        <v>736185269</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A28">
-        <v>668624772</v>
-      </c>
-      <c r="B28" t="s">
-        <v>2</v>
+        <v>762248155</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A29">
-        <v>652185657</v>
-      </c>
-      <c r="B29" t="s">
-        <v>4</v>
+        <v>760737969</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A30">
-        <v>809983665</v>
-      </c>
-      <c r="B30" t="s">
-        <v>4</v>
+        <v>744054168</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A31">
-        <v>799847102</v>
-      </c>
-      <c r="B31" t="s">
-        <v>4</v>
+        <v>743681573</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A32">
-        <v>699897058</v>
-      </c>
-      <c r="B32" t="s">
-        <v>4</v>
+        <v>730765934</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A33">
-        <v>786596324</v>
-      </c>
-      <c r="B33" t="s">
-        <v>4</v>
+        <v>707734350</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A34">
-        <v>764793042</v>
-      </c>
-      <c r="B34" t="s">
-        <v>4</v>
+        <v>700968732</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A35">
-        <v>759079811</v>
-      </c>
-      <c r="B35" t="s">
-        <v>4</v>
+        <v>698712381</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A36">
-        <v>756972158</v>
-      </c>
-      <c r="B36" t="s">
-        <v>4</v>
+        <v>690782754</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A37">
-        <v>735486544</v>
-      </c>
-      <c r="B37" t="s">
-        <v>4</v>
+        <v>671445280</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A38">
-        <v>695334965</v>
-      </c>
-      <c r="B38" t="s">
-        <v>4</v>
+        <v>673342949</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A39">
-        <v>691830156</v>
-      </c>
-      <c r="B39" t="s">
-        <v>4</v>
+        <v>671668204</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A40">
-        <v>598088478</v>
-      </c>
-      <c r="B40" t="s">
-        <v>4</v>
+        <v>668229093</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A41">
-        <v>614118622</v>
-      </c>
-      <c r="B41" t="s">
-        <v>5</v>
+        <v>665376137</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A42">
-        <v>806930396</v>
-      </c>
-      <c r="B42" t="s">
-        <v>5</v>
+        <v>630059891</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A43">
-        <v>697174773</v>
-      </c>
-      <c r="B43" t="s">
-        <v>5</v>
+        <v>607132812</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A44">
-        <v>734618071</v>
-      </c>
-      <c r="B44" t="s">
-        <v>5</v>
+        <v>592771723</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A45">
-        <v>764485573</v>
-      </c>
-      <c r="B45" t="s">
-        <v>5</v>
+        <v>581313404</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A46">
-        <v>611296272</v>
-      </c>
-      <c r="B46" t="s">
-        <v>5</v>
+        <v>650354958</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A47">
-        <v>669846283</v>
-      </c>
-      <c r="B47" t="s">
-        <v>3</v>
+        <v>718681509</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A48">
-        <v>788451536</v>
-      </c>
-      <c r="B48" t="s">
-        <v>6</v>
+        <v>673788265</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A49">
-        <v>787237597</v>
-      </c>
-      <c r="B49" t="s">
-        <v>2</v>
+        <v>625225515</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A50">
-        <v>799908011</v>
-      </c>
-      <c r="B50" t="s">
+        <v>679179170</v>
+      </c>
+      <c r="B50" s="3" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A51">
-        <v>176424087</v>
-      </c>
-      <c r="B51" t="s">
+        <v>788335499</v>
+      </c>
+      <c r="B51" s="3" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A52">
-        <v>637095526</v>
-      </c>
-      <c r="B52" t="s">
+        <v>804049926</v>
+      </c>
+      <c r="B52" s="3" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A53">
-        <v>799898899</v>
-      </c>
-      <c r="B53" t="s">
+        <v>688426638</v>
+      </c>
+      <c r="B53" s="3" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A54">
-        <v>590025304</v>
-      </c>
-      <c r="B54" t="s">
-        <v>4</v>
+        <v>176119430</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A55">
-        <v>803147069</v>
+        <v>804262578</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A56">
-        <v>686942172</v>
+        <v>782793735</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A57">
-        <v>802429153</v>
+        <v>719068623</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A58">
-        <v>780964098</v>
+        <v>690251503</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A59">
-        <v>643073228</v>
-      </c>
-      <c r="B59" s="3" t="s">
-        <v>2</v>
-      </c>
+      <c r="B59" s="3"/>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A60">
-        <v>682832088</v>
-      </c>
-      <c r="B60" s="3" t="s">
-        <v>2</v>
-      </c>
+      <c r="B60" s="3"/>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A61">
-        <v>682113315</v>
-      </c>
-      <c r="B61" s="3" t="s">
-        <v>2</v>
-      </c>
+      <c r="B61" s="3"/>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A62">
-        <v>676416179</v>
-      </c>
-      <c r="B62" s="3" t="s">
-        <v>2</v>
-      </c>
+      <c r="B62" s="3"/>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A63">
-        <v>671084808</v>
-      </c>
-      <c r="B63" s="3" t="s">
-        <v>2</v>
-      </c>
+      <c r="B63" s="3"/>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A64">
-        <v>658267095</v>
-      </c>
-      <c r="B64" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A65">
-        <v>656245515</v>
-      </c>
-      <c r="B65" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A66">
-        <v>654771280</v>
-      </c>
-      <c r="B66" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A67">
-        <v>650380581</v>
-      </c>
-      <c r="B67" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A68">
-        <v>649776832</v>
-      </c>
-      <c r="B68" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A69">
-        <v>612943138</v>
-      </c>
-      <c r="B69" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A70">
-        <v>788277832</v>
-      </c>
-      <c r="B70" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A71">
-        <v>690808039</v>
-      </c>
-      <c r="B71" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A72">
-        <v>726742053</v>
-      </c>
-      <c r="B72" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A73">
-        <v>719294443</v>
-      </c>
-      <c r="B73" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A74">
-        <v>717338242</v>
-      </c>
-      <c r="B74" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A75">
-        <v>709670768</v>
-      </c>
-      <c r="B75" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A76">
-        <v>702119318</v>
-      </c>
-      <c r="B76" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A77">
-        <v>690059088</v>
-      </c>
-      <c r="B77" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A78">
-        <v>174472476</v>
-      </c>
-      <c r="B78" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A79">
-        <v>174456396</v>
-      </c>
-      <c r="B79" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A80">
-        <v>802114938</v>
-      </c>
-      <c r="B80" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A81">
-        <v>801222518</v>
-      </c>
-      <c r="B81" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A82">
-        <v>800573655</v>
-      </c>
-      <c r="B82" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A83">
-        <v>799130970</v>
-      </c>
-      <c r="B83" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A84">
-        <v>787090004</v>
-      </c>
-      <c r="B84" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A85">
-        <v>751967989</v>
-      </c>
-      <c r="B85" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A86">
-        <v>740071661</v>
-      </c>
-      <c r="B86" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A87">
-        <v>738992332</v>
-      </c>
-      <c r="B87" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A88">
-        <v>737636559</v>
-      </c>
-      <c r="B88" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A89">
-        <v>734786845</v>
-      </c>
-      <c r="B89" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A90">
-        <v>732683648</v>
-      </c>
-      <c r="B90" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A91">
-        <v>732434240</v>
-      </c>
-      <c r="B91" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A92">
-        <v>737815534</v>
-      </c>
-      <c r="B92" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A93">
-        <v>707095273</v>
-      </c>
-      <c r="B93" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A94">
-        <v>730597196</v>
-      </c>
-      <c r="B94" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="95" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A95">
-        <v>723366237</v>
-      </c>
-      <c r="B95" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="96" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A96">
-        <v>703566152</v>
-      </c>
-      <c r="B96" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A97">
-        <v>622075947</v>
-      </c>
-      <c r="B97" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="98" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A98">
-        <v>657700542</v>
-      </c>
-      <c r="B98" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="99" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A99">
-        <v>663707754</v>
-      </c>
-      <c r="B99" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="100" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A100">
-        <v>637848056</v>
-      </c>
-      <c r="B100" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="101" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A101">
-        <v>627080306</v>
-      </c>
-      <c r="B101" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="102" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A102">
-        <v>625290063</v>
-      </c>
-      <c r="B102" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="103" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A103">
-        <v>600735264</v>
-      </c>
-      <c r="B103" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="104" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A104">
-        <v>599356155</v>
-      </c>
-      <c r="B104" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="105" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A105">
-        <v>597364649</v>
-      </c>
-      <c r="B105" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="106" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A106">
-        <v>789909029</v>
-      </c>
-      <c r="B106" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="107" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A107">
-        <v>810386577</v>
-      </c>
-      <c r="B107" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="108" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A108">
-        <v>791960895</v>
-      </c>
-      <c r="B108" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="109" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A109">
-        <v>800734745</v>
-      </c>
-      <c r="B109" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="110" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A110">
-        <v>801049408</v>
-      </c>
-      <c r="B110" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="111" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A111">
-        <v>774097848</v>
-      </c>
-      <c r="B111" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="112" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A112">
-        <v>772506519</v>
-      </c>
-      <c r="B112" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="113" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A113">
-        <v>765480052</v>
-      </c>
-      <c r="B113" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="114" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A114">
-        <v>764151878</v>
-      </c>
-      <c r="B114" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="115" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A115">
-        <v>760398374</v>
-      </c>
-      <c r="B115" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="116" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A116">
-        <v>756596676</v>
-      </c>
-      <c r="B116" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="117" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A117">
-        <v>743058822</v>
-      </c>
-      <c r="B117" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="118" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A118">
-        <v>740774652</v>
-      </c>
-      <c r="B118" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="119" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A119">
-        <v>732895481</v>
-      </c>
-      <c r="B119" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="120" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A120">
-        <v>705490690</v>
-      </c>
-      <c r="B120" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="121" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A121">
-        <v>715698852</v>
-      </c>
-      <c r="B121" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="122" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A122">
-        <v>701261772</v>
-      </c>
-      <c r="B122" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="123" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A123">
-        <v>695880637</v>
-      </c>
-      <c r="B123" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="124" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A124">
-        <v>596527162</v>
-      </c>
-      <c r="B124" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="125" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A125">
-        <v>677811089</v>
-      </c>
-      <c r="B125" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="126" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A126">
-        <v>684654225</v>
-      </c>
-      <c r="B126" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="127" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A127">
-        <v>782208460</v>
-      </c>
-      <c r="B127" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="128" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A128">
-        <v>803557085</v>
-      </c>
-      <c r="B128" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="129" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A129">
-        <v>769784004</v>
-      </c>
-      <c r="B129" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="130" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A130">
-        <v>754772899</v>
-      </c>
-      <c r="B130" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="131" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A131">
-        <v>799320142</v>
-      </c>
-      <c r="B131" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="132" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A132">
-        <v>799229657</v>
-      </c>
-      <c r="B132" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="133" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A133">
-        <v>788230534</v>
-      </c>
-      <c r="B133" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="134" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A134">
-        <v>787280886</v>
-      </c>
-      <c r="B134" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="135" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A135">
-        <v>779293004</v>
-      </c>
-      <c r="B135" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="136" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A136">
-        <v>803946155</v>
-      </c>
-      <c r="B136" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="137" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A137">
-        <v>574889675</v>
-      </c>
-      <c r="B137" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="138" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A138">
-        <v>689106098</v>
-      </c>
-      <c r="B138" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="139" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A139">
-        <v>742730694</v>
-      </c>
-      <c r="B139" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="140" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A140">
-        <v>622232241</v>
-      </c>
-      <c r="B140" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="141" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A141">
-        <v>678687660</v>
-      </c>
-      <c r="B141" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="142" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A142">
-        <v>585366408</v>
-      </c>
-      <c r="B142" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="143" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A143">
-        <v>801354063</v>
-      </c>
-      <c r="B143" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="144" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A144">
-        <v>170181675</v>
-      </c>
-      <c r="B144" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="145" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A145">
-        <v>720693740</v>
-      </c>
-      <c r="B145" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="146" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A146">
-        <v>171383452</v>
-      </c>
-      <c r="B146" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="147" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A147">
-        <v>170181808</v>
-      </c>
-      <c r="B147" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="148" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A148">
-        <v>802911556</v>
-      </c>
-      <c r="B148" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="149" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A149">
-        <v>802446751</v>
-      </c>
-      <c r="B149" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="150" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A150">
-        <v>784967089</v>
-      </c>
-      <c r="B150" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="151" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A151">
-        <v>672342437</v>
-      </c>
-      <c r="B151" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="152" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A152">
-        <v>658970151</v>
-      </c>
-      <c r="B152" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="153" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A153">
-        <v>600936128</v>
-      </c>
-      <c r="B153" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="154" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A154">
-        <v>755884222</v>
-      </c>
-      <c r="B154" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="155" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A155">
-        <v>736017868</v>
-      </c>
-      <c r="B155" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="156" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A156">
-        <v>742123676</v>
-      </c>
-      <c r="B156" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="157" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A157">
-        <v>723391581</v>
-      </c>
-      <c r="B157" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="158" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A158">
-        <v>702637483</v>
-      </c>
-      <c r="B158" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="159" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A159">
-        <v>623813825</v>
-      </c>
-      <c r="B159" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="160" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A160">
-        <v>666998723</v>
-      </c>
-      <c r="B160" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="161" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A161">
-        <v>711500854</v>
-      </c>
-      <c r="B161" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="162" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A162">
-        <v>663954802</v>
-      </c>
-      <c r="B162" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="163" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A163">
-        <v>617081892</v>
-      </c>
-      <c r="B163" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="164" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A164">
-        <v>628586467</v>
-      </c>
-      <c r="B164" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="165" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A165">
-        <v>801787957</v>
-      </c>
-      <c r="B165" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="166" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A166">
-        <v>752705040</v>
-      </c>
-      <c r="B166" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="167" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A167">
-        <v>800006755</v>
-      </c>
-      <c r="B167" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="168" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A168">
-        <v>802666309</v>
-      </c>
-      <c r="B168" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="169" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A169">
-        <v>596346613</v>
-      </c>
-      <c r="B169" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="170" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A170">
-        <v>586618724</v>
-      </c>
-      <c r="B170" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="171" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A171">
-        <v>604044325</v>
-      </c>
-      <c r="B171" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="172" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A172">
-        <v>665208710</v>
-      </c>
-      <c r="B172" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="173" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A173">
-        <v>684725074</v>
-      </c>
-      <c r="B173" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="174" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A174">
-        <v>653376446</v>
-      </c>
-      <c r="B174" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="175" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A175">
-        <v>802340426</v>
-      </c>
-      <c r="B175" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="176" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A176">
-        <v>803900897</v>
-      </c>
-      <c r="B176" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="177" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A177">
-        <v>799517721</v>
-      </c>
-      <c r="B177" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="178" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A178">
-        <v>784887352</v>
-      </c>
-      <c r="B178" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="179" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A179">
-        <v>776283131</v>
-      </c>
-      <c r="B179" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="180" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A180">
-        <v>780254722</v>
-      </c>
-      <c r="B180" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="181" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A181">
-        <v>752014377</v>
-      </c>
-      <c r="B181" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="182" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A182">
-        <v>735625398</v>
-      </c>
-      <c r="B182" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="183" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A183">
-        <v>723216754</v>
-      </c>
-      <c r="B183" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="184" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A184">
-        <v>703034417</v>
-      </c>
-      <c r="B184" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="185" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A185">
-        <v>762930307</v>
-      </c>
-      <c r="B185" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="186" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A186">
-        <v>801376850</v>
-      </c>
-      <c r="B186" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="187" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B64" s="3"/>
+    </row>
+    <row r="65" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B65" s="3"/>
+    </row>
+    <row r="66" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B66" s="3"/>
+    </row>
+    <row r="67" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B67" s="3"/>
+    </row>
+    <row r="68" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B68" s="3"/>
+    </row>
+    <row r="69" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B69" s="3"/>
+    </row>
+    <row r="70" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B70" s="3"/>
+    </row>
+    <row r="71" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B71" s="3"/>
+    </row>
+    <row r="72" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B72" s="3"/>
+    </row>
+    <row r="73" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B73" s="3"/>
+    </row>
+    <row r="74" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B74" s="3"/>
+    </row>
+    <row r="75" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B75" s="3"/>
+    </row>
+    <row r="76" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B76" s="3"/>
+    </row>
+    <row r="77" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B77" s="3"/>
+    </row>
+    <row r="78" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B78" s="3"/>
+    </row>
+    <row r="79" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B79" s="3"/>
+    </row>
+    <row r="80" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B80" s="3"/>
+    </row>
+    <row r="81" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B81" s="3"/>
+    </row>
+    <row r="82" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B82" s="3"/>
+    </row>
+    <row r="83" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B83" s="3"/>
+    </row>
+    <row r="84" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B84" s="3"/>
+    </row>
+    <row r="85" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B85" s="3"/>
+    </row>
+    <row r="86" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B86" s="3"/>
+    </row>
+    <row r="87" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B87" s="3"/>
+    </row>
+    <row r="88" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B88" s="3"/>
+    </row>
+    <row r="89" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B89" s="3"/>
+    </row>
+    <row r="90" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B90" s="3"/>
+    </row>
+    <row r="91" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B91" s="3"/>
+    </row>
+    <row r="92" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B92" s="3"/>
+    </row>
+    <row r="93" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B93" s="3"/>
+    </row>
+    <row r="94" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B94" s="3"/>
+    </row>
+    <row r="95" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B95" s="3"/>
+    </row>
+    <row r="96" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B96" s="3"/>
+    </row>
+    <row r="97" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B97" s="3"/>
+    </row>
+    <row r="98" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B98" s="3"/>
+    </row>
+    <row r="99" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B99" s="3"/>
+    </row>
+    <row r="100" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B100" s="3"/>
+    </row>
+    <row r="101" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B101" s="3"/>
+    </row>
+    <row r="102" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B102" s="3"/>
+    </row>
+    <row r="103" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B103" s="3"/>
+    </row>
+    <row r="104" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B104" s="3"/>
+    </row>
+    <row r="105" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B105" s="3"/>
+    </row>
+    <row r="106" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B106" s="3"/>
+    </row>
+    <row r="107" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B107" s="3"/>
+    </row>
+    <row r="108" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B108" s="3"/>
+    </row>
+    <row r="109" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B109" s="3"/>
+    </row>
+    <row r="110" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B110" s="3"/>
+    </row>
+    <row r="111" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B111" s="3"/>
+    </row>
+    <row r="112" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B112" s="3"/>
+    </row>
+    <row r="113" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B113" s="3"/>
+    </row>
+    <row r="114" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B114" s="3"/>
+    </row>
+    <row r="115" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B115" s="3"/>
+    </row>
+    <row r="116" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B116" s="3"/>
+    </row>
+    <row r="117" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B117" s="3"/>
+    </row>
+    <row r="118" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B118" s="3"/>
+    </row>
+    <row r="119" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B119" s="3"/>
+    </row>
+    <row r="120" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B120" s="3"/>
+    </row>
+    <row r="121" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B121" s="3"/>
+    </row>
+    <row r="122" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B122" s="3"/>
+    </row>
+    <row r="123" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B123" s="3"/>
+    </row>
+    <row r="124" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B124" s="3"/>
+    </row>
+    <row r="125" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B125" s="3"/>
+    </row>
+    <row r="126" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B126" s="3"/>
+    </row>
+    <row r="127" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B127" s="3"/>
+    </row>
+    <row r="128" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B128" s="3"/>
+    </row>
+    <row r="129" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B129" s="3"/>
+    </row>
+    <row r="130" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B130" s="3"/>
+    </row>
+    <row r="131" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B131" s="3"/>
+    </row>
+    <row r="132" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B132" s="3"/>
+    </row>
+    <row r="133" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B133" s="3"/>
+    </row>
+    <row r="134" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B134" s="3"/>
+    </row>
+    <row r="135" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B135" s="3"/>
+    </row>
+    <row r="136" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B136" s="3"/>
+    </row>
+    <row r="137" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B137" s="3"/>
+    </row>
+    <row r="138" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B138" s="3"/>
+    </row>
+    <row r="139" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B139" s="3"/>
+    </row>
+    <row r="140" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B140" s="3"/>
+    </row>
+    <row r="141" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B141" s="3"/>
+    </row>
+    <row r="142" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B142" s="3"/>
+    </row>
+    <row r="143" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B143" s="3"/>
+    </row>
+    <row r="144" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B144" s="3"/>
+    </row>
+    <row r="145" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B145" s="3"/>
+    </row>
+    <row r="146" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B146" s="3"/>
+    </row>
+    <row r="147" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B147" s="3"/>
+    </row>
+    <row r="148" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B148" s="3"/>
+    </row>
+    <row r="149" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B149" s="3"/>
+    </row>
+    <row r="150" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B150" s="3"/>
+    </row>
+    <row r="151" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B151" s="3"/>
+    </row>
+    <row r="152" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B152" s="3"/>
+    </row>
+    <row r="153" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B153" s="3"/>
+    </row>
+    <row r="154" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B154" s="3"/>
+    </row>
+    <row r="155" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B155" s="3"/>
+    </row>
+    <row r="156" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B156" s="3"/>
+    </row>
+    <row r="157" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B157" s="3"/>
+    </row>
+    <row r="158" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B158" s="3"/>
+    </row>
+    <row r="159" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B159" s="3"/>
+    </row>
+    <row r="160" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B160" s="3"/>
+    </row>
+    <row r="161" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B161" s="3"/>
+    </row>
+    <row r="162" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B162" s="3"/>
+    </row>
+    <row r="163" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B163" s="3"/>
+    </row>
+    <row r="164" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B164" s="3"/>
+    </row>
+    <row r="165" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B165" s="3"/>
+    </row>
+    <row r="166" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B166" s="3"/>
+    </row>
+    <row r="167" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B167" s="3"/>
+    </row>
+    <row r="168" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B168" s="3"/>
+    </row>
+    <row r="169" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B169" s="3"/>
+    </row>
+    <row r="170" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B170" s="3"/>
+    </row>
+    <row r="171" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B171" s="3"/>
+    </row>
+    <row r="172" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B172" s="3"/>
+    </row>
+    <row r="173" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B173" s="3"/>
+    </row>
+    <row r="174" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B174" s="3"/>
+    </row>
+    <row r="175" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B175" s="3"/>
+    </row>
+    <row r="176" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B176" s="3"/>
+    </row>
+    <row r="177" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B177" s="3"/>
+    </row>
+    <row r="178" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B178" s="3"/>
+    </row>
+    <row r="179" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B179" s="3"/>
+    </row>
+    <row r="180" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B180" s="3"/>
+    </row>
+    <row r="181" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B181" s="3"/>
+    </row>
+    <row r="182" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B182" s="3"/>
+    </row>
+    <row r="183" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B183" s="3"/>
+    </row>
+    <row r="184" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B184" s="3"/>
+    </row>
+    <row r="185" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B185" s="3"/>
+    </row>
+    <row r="186" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B186" s="3"/>
+    </row>
+    <row r="187" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B187" s="3"/>
     </row>
-    <row r="188" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="188" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B188" s="3"/>
     </row>
-    <row r="189" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="189" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B189" s="3"/>
     </row>
-    <row r="190" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="190" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B190" s="3"/>
     </row>
-    <row r="191" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="191" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B191" s="3"/>
     </row>
-    <row r="192" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="192" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B192" s="3"/>
     </row>
     <row r="193" spans="2:2" x14ac:dyDescent="0.2">
@@ -5428,19 +4772,22 @@
       <c r="B1335" s="3"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A187:A1048576 A1">
-    <cfRule type="duplicateValues" dxfId="4" priority="17"/>
+  <conditionalFormatting sqref="A59:A186">
+    <cfRule type="duplicateValues" dxfId="5" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A187:A998">
-    <cfRule type="duplicateValues" dxfId="3" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="24"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A187:A1048576 A1">
+    <cfRule type="duplicateValues" dxfId="3" priority="18"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A999:A1167">
-    <cfRule type="duplicateValues" dxfId="2" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="23"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1168:A1335">
-    <cfRule type="duplicateValues" dxfId="1" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="22"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A2:A186">
+  <conditionalFormatting sqref="A2:A58">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
